--- a/ProyectoSoftwareSistemas/bin/Debug/output/bloq1_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/bloq1_ArchivoIntermedio.xlsx
@@ -9,6 +9,7 @@
     <x:sheet name="ArchivoIntermedio" sheetId="1" r:id="rId2"/>
     <x:sheet name="ProgramaObjeto" sheetId="2" r:id="rId3"/>
     <x:sheet name="TABBLK" sheetId="3" r:id="rId4"/>
+    <x:sheet name="TABSIM" sheetId="4" r:id="rId5"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -84,7 +85,7 @@
     <x:t>Simple</x:t>
   </x:si>
   <x:si>
-    <x:t>172FFD</x:t>
+    <x:t>172035</x:t>
   </x:si>
   <x:si>
     <x:t>0003</x:t>
@@ -132,10 +133,7 @@
     <x:t>LENGTH</x:t>
   </x:si>
   <x:si>
-    <x:t>Hex inválido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>036FFF</x:t>
+    <x:t>03202E</x:t>
   </x:si>
   <x:si>
     <x:t>USE</x:t>
@@ -219,7 +217,7 @@
     <x:t>#INIC</x:t>
   </x:si>
   <x:si>
-    <x:t>75100002*</x:t>
+    <x:t>75101025*</x:t>
   </x:si>
   <x:si>
     <x:t>INPUT</x:t>
@@ -267,7 +265,7 @@
     <x:t>RETADR+BUFFEND-BUFFER</x:t>
   </x:si>
   <x:si>
-    <x:t>Error: Símbolos de diferentes bloques en EQU | Expresión relativa inválida</x:t>
+    <x:t xml:space="preserve">Error: Símbolos de diferentes bloques en EQU | </x:t>
   </x:si>
   <x:si>
     <x:t>0013</x:t>
@@ -276,7 +274,7 @@
     <x:t>LDT</x:t>
   </x:si>
   <x:si>
-    <x:t>776FFF</x:t>
+    <x:t>772025</x:t>
   </x:si>
   <x:si>
     <x:t>0016</x:t>
@@ -288,10 +286,7 @@
     <x:t>RETADR+BUFFEND-BUFFER+10</x:t>
   </x:si>
   <x:si>
-    <x:t>Expresión relativa inválida</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FFFFFF</x:t>
+    <x:t>001042*</x:t>
   </x:si>
   <x:si>
     <x:t>0019</x:t>
@@ -312,10 +307,10 @@
     <x:t>HBLOQUE00000000001C</x:t>
   </x:si>
   <x:si>
-    <x:t>T0000000D172FFD4B200729101000036FFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00000D18B41075100002F1B41001000A4F0000776FFFFFFFFF00100A</x:t>
+    <x:t>T0000000D1720354B20072910100003202E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00000D18B41075101025F1B41001000A4F000077202500104200100A</x:t>
   </x:si>
   <x:si>
     <x:t>M00000705+BLOQUE</x:t>
@@ -324,6 +319,9 @@
     <x:t>M00001005+BLOQUE</x:t>
   </x:si>
   <x:si>
+    <x:t>M00001606+BLOQUE</x:t>
+  </x:si>
+  <x:si>
     <x:t>E000002</x:t>
   </x:si>
   <x:si>
@@ -355,6 +353,42 @@
   </x:si>
   <x:si>
     <x:t>1028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Simbolo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Direccion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tipo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Relativo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bloque</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8D80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FFFF</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -894,10 +928,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
@@ -914,10 +948,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>14</x:v>
@@ -946,10 +980,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>14</x:v>
@@ -978,10 +1012,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>14</x:v>
@@ -1010,10 +1044,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
         <x:v>14</x:v>
@@ -1039,13 +1073,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E11" s="0" t="s">
+      <x:c r="F11" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>14</x:v>
@@ -1068,16 +1102,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="E12" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="s">
+      <x:c r="F12" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>14</x:v>
@@ -1100,16 +1134,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>14</x:v>
@@ -1132,16 +1166,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>14</x:v>
@@ -1164,16 +1198,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>14</x:v>
@@ -1196,13 +1230,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>16</x:v>
@@ -1228,28 +1262,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F17" s="0" t="s">
+      <x:c r="G17" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G17" s="0" t="s">
+      <x:c r="H17" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H17" s="0" t="s">
+      <x:c r="I17" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
@@ -1260,16 +1294,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
+      <x:c r="F18" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>31</x:v>
@@ -1281,7 +1315,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
@@ -1298,10 +1332,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>14</x:v>
@@ -1327,13 +1361,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="E20" s="0" t="s">
+      <x:c r="F20" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>14</x:v>
@@ -1345,7 +1379,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
@@ -1362,10 +1396,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>14</x:v>
@@ -1394,22 +1428,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F22" s="0" t="s">
+      <x:c r="G22" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G22" s="0" t="s">
+      <x:c r="H22" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H22" s="0" t="s">
+      <x:c r="I22" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="I22" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
@@ -1420,16 +1454,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>20</x:v>
@@ -1441,7 +1475,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
@@ -1458,10 +1492,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
         <x:v>14</x:v>
@@ -1487,10 +1521,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>16</x:v>
@@ -1505,7 +1539,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
@@ -1519,13 +1553,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
         <x:v>14</x:v>
@@ -1534,7 +1568,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
         <x:v>17</x:v>
@@ -1548,13 +1582,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>16</x:v>
@@ -1580,13 +1614,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>37</x:v>
@@ -1598,10 +1632,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
@@ -1612,16 +1646,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
+      <x:c r="F29" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
         <x:v>14</x:v>
@@ -1630,10 +1664,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10">
@@ -1644,16 +1678,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
         <x:v>14</x:v>
@@ -1665,7 +1699,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
@@ -1676,16 +1710,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
         <x:v>14</x:v>
@@ -1714,7 +1748,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A6"/>
+  <x:dimension ref="A1:A7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="61.996339" style="0" customWidth="1"/>
@@ -1722,32 +1756,37 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:1">
+      <x:c r="A7" s="0" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1774,16 +1813,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="C1" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="D1" s="0" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="D1" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1791,10 +1830,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1805,13 +1844,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
@@ -1819,13 +1858,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
@@ -1833,13 +1872,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
@@ -1847,13 +1886,292 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E15"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.853482" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5">
+      <x:c r="A1" s="0" t="s">
         <x:v>112</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
+      <x:c r="A2" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
+      <x:c r="A7" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
+      <x:c r="A8" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
+      <x:c r="A9" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5">
+      <x:c r="A10" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:5">
+      <x:c r="A11" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:5">
+      <x:c r="A12" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:5">
+      <x:c r="A13" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:5">
+      <x:c r="A14" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:5">
+      <x:c r="A15" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/ProyectoSoftwareSistemas/bin/Debug/output/bloq1_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/bloq1_ArchivoIntermedio.xlsx
@@ -85,7 +85,7 @@
     <x:t>Simple</x:t>
   </x:si>
   <x:si>
-    <x:t>172035</x:t>
+    <x:t>172019</x:t>
   </x:si>
   <x:si>
     <x:t>0003</x:t>
@@ -118,7 +118,7 @@
     <x:t>Inmediato</x:t>
   </x:si>
   <x:si>
-    <x:t>29101000*</x:t>
+    <x:t>29101000</x:t>
   </x:si>
   <x:si>
     <x:t>000A</x:t>
@@ -133,7 +133,7 @@
     <x:t>LENGTH</x:t>
   </x:si>
   <x:si>
-    <x:t>03202E</x:t>
+    <x:t>032012</x:t>
   </x:si>
   <x:si>
     <x:t>USE</x:t>
@@ -274,7 +274,7 @@
     <x:t>LDT</x:t>
   </x:si>
   <x:si>
-    <x:t>772025</x:t>
+    <x:t>772009</x:t>
   </x:si>
   <x:si>
     <x:t>0016</x:t>
@@ -286,7 +286,7 @@
     <x:t>RETADR+BUFFEND-BUFFER+10</x:t>
   </x:si>
   <x:si>
-    <x:t>001042*</x:t>
+    <x:t>001026*</x:t>
   </x:si>
   <x:si>
     <x:t>0019</x:t>
@@ -304,16 +304,25 @@
     <x:t>END</x:t>
   </x:si>
   <x:si>
-    <x:t>HBLOQUE00000000001C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T0000000D1720354B20072910100003202E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00000D18B41075101025F1B41001000A4F000077202500104200100A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M00000705+BLOQUE</x:t>
+    <x:t>HBLOQUE00000000102B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T0000000D1720194B200729101000032012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00000D06B41075101025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00002201F1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00102305B41001000A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T001028034F0000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T0000130977200900102600100A</x:t>
   </x:si>
   <x:si>
     <x:t>M00001005+BLOQUE</x:t>
@@ -322,7 +331,7 @@
     <x:t>M00001606+BLOQUE</x:t>
   </x:si>
   <x:si>
-    <x:t>E000002</x:t>
+    <x:t>E001025</x:t>
   </x:si>
   <x:si>
     <x:t>No. Bloque</x:t>
@@ -1748,10 +1757,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A7"/>
+  <x:dimension ref="A1:A10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="61.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
@@ -1787,6 +1796,21 @@
     <x:row r="7" spans="1:1">
       <x:c r="A7" s="0" t="s">
         <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:1">
+      <x:c r="A8" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:1">
+      <x:c r="A9" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:1">
+      <x:c r="A10" s="0" t="s">
+        <x:v>104</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1813,16 +1837,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1830,7 +1854,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>93</x:v>
@@ -1847,7 +1871,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>93</x:v>
@@ -1864,7 +1888,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
@@ -1875,10 +1899,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
@@ -1892,7 +1916,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1921,19 +1945,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1944,13 +1968,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1961,13 +1985,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -1978,10 +2002,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>40</x:v>
@@ -1995,10 +2019,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>40</x:v>
@@ -2012,10 +2036,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>43</x:v>
@@ -2026,13 +2050,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>43</x:v>
@@ -2046,10 +2070,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>43</x:v>
@@ -2063,10 +2087,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>43</x:v>
@@ -2077,13 +2101,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>43</x:v>
@@ -2097,13 +2121,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
@@ -2114,10 +2138,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>40</x:v>
@@ -2131,10 +2155,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>71</x:v>
@@ -2148,10 +2172,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>76</x:v>
@@ -2162,13 +2186,13 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>76</x:v>
